--- a/Assets/02Script/Table/EventAfter.xlsx
+++ b/Assets/02Script/Table/EventAfter.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>EventID</t>
   </si>
@@ -75,11 +75,21 @@
     <t>E006</t>
   </si>
   <si>
+    <t>아기침대 아래 서랍 발견</t>
+  </si>
+  <si>
+    <t>&lt;b&gt;축복&lt;/b&gt;의 아래...  "그" 아가씨가 &lt;b&gt;축복&lt;/b&gt;이었던 거군.
+일기에서 그랬지. &lt;i&gt; 앞으로 나아갈 수 있는 길 ""&lt;/i&gt;.</t>
+  </si>
+  <si>
+    <t>E007</t>
+  </si>
+  <si>
     <t>마지막 상자를 열었을 때</t>
   </si>
   <si>
     <t>아까 봤던 열쇠와 비슷하게 생긴 열쇠다.
-일기에서 그랬지. &lt;i&gt;" 앞으로 나아갈 수 있는 길 "&lt;/i&gt;</t>
+그렇다면 ...</t>
   </si>
 </sst>
 </file>
@@ -424,6 +434,17 @@
         <v>20</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
